--- a/cypress/downloads/funding-transactions_28-07-2026_to_28-08-2026.xlsx
+++ b/cypress/downloads/funding-transactions_28-07-2026_to_28-08-2026.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -815,269 +815,9 @@
         <v>Successful</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>30 Jul, 2026 17:50:32</v>
-      </c>
-      <c r="B17" t="str">
-        <v>1.00</v>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v>692.09</v>
-      </c>
-      <c r="E17" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F17" t="str">
-        <v>DAMILOLA BLESSING OLAIYA</v>
-      </c>
-      <c r="G17" t="str">
-        <v>JIN-S15324446841_XFER-C</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>30 Jul, 2026 15:10:24</v>
-      </c>
-      <c r="B18" t="str">
-        <v>1,000.00</v>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v>1060.09</v>
-      </c>
-      <c r="E18" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F18" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G18" t="str">
-        <v>100004260730141001166801367472-C</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>30 Jul, 2026 15:03:21</v>
-      </c>
-      <c r="B19" t="str">
-        <v>50.00</v>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v>60.09</v>
-      </c>
-      <c r="E19" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F19" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G19" t="str">
-        <v>000014260730150257235979836182-C</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>30 Jul, 2026 13:51:27</v>
-      </c>
-      <c r="B20" t="str">
-        <v>5.00</v>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>71.09</v>
-      </c>
-      <c r="E20" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F20" t="str">
-        <v>OLUMUYIWA EMMANUEL AKINTADE</v>
-      </c>
-      <c r="G20" t="str">
-        <v>JIN-S28476482659_XFER-C</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>30 Jul, 2026 13:22:34</v>
-      </c>
-      <c r="B21" t="str">
-        <v>20.00</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v>66.09</v>
-      </c>
-      <c r="E21" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F21" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G21" t="str">
-        <v>JIN-B32134012645-R-FEE-C</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>30 Jul, 2026 13:22:33</v>
-      </c>
-      <c r="B22" t="str">
-        <v>20.00</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v>46.09</v>
-      </c>
-      <c r="E22" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F22" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G22" t="str">
-        <v>JIN-B14772588082-R-FEE-C</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>30 Jul, 2026 13:17:38</v>
-      </c>
-      <c r="B23" t="str">
-        <v>20.00</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>26.09</v>
-      </c>
-      <c r="E23" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F23" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G23" t="str">
-        <v>JIN-B47577088838-R-FEE-C</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>30 Jul, 2026 13:13:09</v>
-      </c>
-      <c r="B24" t="str">
-        <v>20.00</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v>41.09</v>
-      </c>
-      <c r="E24" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F24" t="str">
-        <v>JABARI INC.</v>
-      </c>
-      <c r="G24" t="str">
-        <v>JIN-B7394908340-R-FEE-C</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>30 Jul, 2026 12:27:56</v>
-      </c>
-      <c r="B25" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v>136.09</v>
-      </c>
-      <c r="E25" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F25" t="str">
-        <v>AKINTADE OLUMUYIWA EMMANUEL</v>
-      </c>
-      <c r="G25" t="str">
-        <v>JIN-S38176622702_XFER-C</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>30 Jul, 2026 12:03:01</v>
-      </c>
-      <c r="B26" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v>161.09</v>
-      </c>
-      <c r="E26" t="str">
-        <v>SBP0000829</v>
-      </c>
-      <c r="F26" t="str">
-        <v>7065271387</v>
-      </c>
-      <c r="G26" t="str">
-        <v>JIN-S33828542222_XFER-C</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Successful</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
   </ignoredErrors>
 </worksheet>
 </file>